--- a/output/pdf_financials_xlsx/ATZ.xlsx
+++ b/output/pdf_financials_xlsx/ATZ.xlsx
@@ -2312,31 +2312,31 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>10.245</v>
+        <v>10.971</v>
       </c>
       <c r="C48" s="3" t="n">
         <v>12.743</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>16.005</v>
+        <v>17.733</v>
       </c>
       <c r="E48" s="3" t="n">
         <v>18.422</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>10.88</v>
+        <v>13.037</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>23.452</v>
+        <v>28.171</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>33.564</v>
+        <v>40.019</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>33.101</v>
+        <v>39.52</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>37.27</v>
+        <v>44.325</v>
       </c>
       <c r="K48" s="3" t="n">
         <v>40.029</v>
@@ -7952,7 +7952,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>OtherCurrentAssets</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -8569,7 +8569,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>OtherCurrentAssets</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -9712,7 +9712,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>OtherCurrentAssets</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -10873,7 +10873,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>OtherCurrentAssets</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -12354,7 +12354,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>OtherCurrentAssets</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E97" s="5" t="n">

--- a/output/pdf_financials_xlsx/ATZ.xlsx
+++ b/output/pdf_financials_xlsx/ATZ.xlsx
@@ -1557,25 +1557,25 @@
         <v>27.065</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>34.422</v>
+        <v>59.08</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>38.871</v>
+        <v>66.27800000000001</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>44.569</v>
+        <v>68.05800000000001</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>52.855</v>
+        <v>81.047</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>64.515</v>
+        <v>103.524</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>84.41500000000001</v>
+        <v>102.238</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>111.447</v>
+        <v>102.642</v>
       </c>
     </row>
     <row r="29">
@@ -1597,25 +1597,25 @@
         <v>138.715</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>160.56</v>
+        <v>185.218</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>65.07299999999999</v>
+        <v>92.48</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>264.169</v>
+        <v>287.658</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>316.662</v>
+        <v>344.854</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>179.125</v>
+        <v>218.134</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>374.868</v>
+        <v>392.691</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>628.205</v>
+        <v>619.4</v>
       </c>
     </row>
     <row r="30">
@@ -1637,25 +1637,25 @@
         <v>15.86590811349932</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>16.3738324619183</v>
+        <v>18.88844357829835</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>7.590254781453432</v>
+        <v>10.78706625157613</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>17.67454152532734</v>
+        <v>19.24610104172939</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>14.4223753546818</v>
+        <v>15.7063804010694</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>7.680022295110082</v>
+        <v>9.352541428173302</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>13.69074749316317</v>
+        <v>14.34167046490428</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>16.96866251700364</v>
+        <v>16.73082761683218</v>
       </c>
     </row>
     <row r="31">
@@ -4403,25 +4403,25 @@
         <v>27.065</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>34.422</v>
+        <v>59.08</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>38.871</v>
+        <v>66.27800000000001</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>44.569</v>
+        <v>68.05800000000001</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>52.855</v>
+        <v>81.047</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>64.515</v>
+        <v>103.524</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>84.41500000000001</v>
+        <v>102.238</v>
       </c>
       <c r="L100" s="3" t="n">
-        <v>111.447</v>
+        <v>102.642</v>
       </c>
     </row>
     <row r="101">
@@ -15160,7 +15160,11 @@
           <t>Depreciation on right-of-use assets 8</t>
         </is>
       </c>
-      <c r="D137" t="inlineStr"/>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E137" t="inlineStr">
         <is>
           <t>-</t>
@@ -17820,7 +17824,11 @@
           <t>Depreciation on right-of-use assets 9</t>
         </is>
       </c>
-      <c r="D177" t="inlineStr"/>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E177" t="inlineStr">
         <is>
           <t>-</t>
@@ -19882,7 +19890,11 @@
           <t>Depreciation on right-of-use-assets 8, 17</t>
         </is>
       </c>
-      <c r="D207" t="inlineStr"/>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E207" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/ATZ.xlsx
+++ b/output/pdf_financials_xlsx/ATZ.xlsx
@@ -3214,13 +3214,13 @@
         </is>
       </c>
       <c r="B70" s="3" t="n">
-        <v>0</v>
+        <v>1.774</v>
       </c>
       <c r="C70" s="3" t="n">
-        <v>0</v>
+        <v>0.983</v>
       </c>
       <c r="D70" s="3" t="n">
-        <v>0</v>
+        <v>0.399</v>
       </c>
       <c r="E70" s="3" t="n">
         <v>0</v>
@@ -3254,13 +3254,13 @@
         </is>
       </c>
       <c r="B71" s="3" t="n">
-        <v>11.348</v>
+        <v>13.122</v>
       </c>
       <c r="C71" s="3" t="n">
-        <v>15.288</v>
+        <v>16.271</v>
       </c>
       <c r="D71" s="3" t="n">
-        <v>19.127</v>
+        <v>19.526</v>
       </c>
       <c r="E71" s="3" t="n">
         <v>0</v>
@@ -3414,10 +3414,10 @@
         </is>
       </c>
       <c r="B75" s="3" t="n">
-        <v>12.476</v>
+        <v>10.702</v>
       </c>
       <c r="C75" s="3" t="n">
-        <v>19.988</v>
+        <v>19.005</v>
       </c>
       <c r="D75" s="3" t="n">
         <v>0</v>
@@ -3614,13 +3614,13 @@
         </is>
       </c>
       <c r="B80" s="3" t="n">
-        <v>1.275598587174527</v>
+        <v>1.291342006709146</v>
       </c>
       <c r="C80" s="3" t="n">
-        <v>0.663500456331098</v>
+        <v>0.6683762549105194</v>
       </c>
       <c r="D80" s="3" t="n">
-        <v>0.4150738009317433</v>
+        <v>0.416470365872013</v>
       </c>
       <c r="E80" s="3" t="n">
         <v>0.199364696013187</v>
@@ -5031,37 +5031,37 @@
         </is>
       </c>
       <c r="B116" s="3" t="n">
-        <v>0</v>
+        <v>-0.167</v>
       </c>
       <c r="C116" s="3" t="n">
-        <v>0</v>
+        <v>-1.329</v>
       </c>
       <c r="D116" s="3" t="n">
-        <v>0</v>
+        <v>-5.269</v>
       </c>
       <c r="E116" s="3" t="n">
-        <v>0</v>
+        <v>-5.585</v>
       </c>
       <c r="F116" s="3" t="n">
-        <v>0</v>
+        <v>-2.199</v>
       </c>
       <c r="G116" s="3" t="n">
-        <v>0</v>
+        <v>-0.593</v>
       </c>
       <c r="H116" s="3" t="n">
-        <v>0</v>
+        <v>-1.594</v>
       </c>
       <c r="I116" s="3" t="n">
-        <v>0</v>
+        <v>-2.821</v>
       </c>
       <c r="J116" s="3" t="n">
-        <v>0</v>
+        <v>-2.974</v>
       </c>
       <c r="K116" s="3" t="n">
-        <v>0</v>
+        <v>-21.085</v>
       </c>
       <c r="L116" s="3" t="n">
-        <v>0</v>
+        <v>-7.551</v>
       </c>
     </row>
     <row r="117">
@@ -5825,43 +5825,37 @@
         </is>
       </c>
       <c r="B135" s="3" t="n">
-        <v>29.626</v>
+        <v>29.605</v>
       </c>
       <c r="C135" s="3" t="n">
-        <v>82.33</v>
+        <v>82.295</v>
       </c>
       <c r="D135" s="3" t="n">
-        <v>44.191</v>
+        <v>44.297</v>
       </c>
       <c r="E135" s="3" t="n">
-        <v>40.2</v>
+        <v>39.75</v>
       </c>
       <c r="F135" s="3" t="n">
-        <v>176.454</v>
+        <v>176.485</v>
       </c>
       <c r="G135" s="3" t="n">
-        <v>72.57599999999999</v>
+        <v>75.373</v>
       </c>
       <c r="H135" s="3" t="n">
-        <v>274.34</v>
+        <v>272.926</v>
       </c>
       <c r="I135" s="3" t="n">
-        <v>-47.752</v>
-      </c>
-      <c r="J135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-47.854</v>
+      </c>
+      <c r="J135" s="3" t="n">
+        <v>185.136</v>
+      </c>
+      <c r="K135" s="3" t="n">
+        <v>199.606</v>
+      </c>
+      <c r="L135" s="3" t="n">
+        <v>545.114</v>
       </c>
     </row>
   </sheetData>
@@ -11853,7 +11847,11 @@
           <t>Lease liabilities 8</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr"/>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E90" t="inlineStr">
         <is>
           <t>-</t>
@@ -12914,7 +12912,11 @@
           <t>Lease liabilities 2, 8</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr"/>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E105" t="inlineStr">
         <is>
           <t>-</t>
@@ -14255,7 +14257,11 @@
           <t>Current portion of lease obligations 6</t>
         </is>
       </c>
-      <c r="D124" t="inlineStr"/>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E124" s="5" t="n">
         <v>0.707</v>
       </c>
@@ -14322,7 +14328,11 @@
           <t>Lease obligations 6</t>
         </is>
       </c>
-      <c r="D125" t="inlineStr"/>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E125" s="5" t="n">
         <v>1.774</v>
       </c>
@@ -15903,7 +15913,11 @@
           <t>Net cash generated from (used in) operating activities</t>
         </is>
       </c>
-      <c r="D148" t="inlineStr"/>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E148" t="inlineStr">
         <is>
           <t>-</t>
@@ -16421,7 +16435,11 @@
           <t>Purchase of intangible assets 7</t>
         </is>
       </c>
-      <c r="D156" t="inlineStr"/>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E156" s="5" t="n">
         <v>-0.167</v>
       </c>
@@ -18579,7 +18597,11 @@
           <t>Net cash generated from operating activities</t>
         </is>
       </c>
-      <c r="D188" t="inlineStr"/>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E188" t="inlineStr">
         <is>
           <t>-</t>
@@ -19125,7 +19147,11 @@
           <t>Purchase of intangible assets 8</t>
         </is>
       </c>
-      <c r="D196" t="inlineStr"/>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E196" t="inlineStr">
         <is>
           <t>-</t>
@@ -20582,7 +20608,11 @@
           <t>Net cash generated from operating activities</t>
         </is>
       </c>
-      <c r="D217" t="inlineStr"/>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E217" t="inlineStr">
         <is>
           <t>-</t>
@@ -23981,7 +24011,11 @@
           <t>Net cash generated from operating activities</t>
         </is>
       </c>
-      <c r="D266" t="inlineStr"/>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E266" s="5" t="n">
         <v>57.621</v>
       </c>
